--- a/upload/sa_promotion_result.xlsx
+++ b/upload/sa_promotion_result.xlsx
@@ -1,33 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ROCIO\LEVANTE\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14565"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Final Request Actual Lumpsum" sheetId="1" r:id="rId1"/>
+    <sheet name="Final Request Actual Lumpsum" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Final Request Actual Lumpsum'!$A$1:$BG$9</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="94">
   <si>
     <t>Promotion No</t>
   </si>
@@ -206,6 +196,12 @@
     <t>KAM Code(Editable)</t>
   </si>
   <si>
+    <t>PR-NTSO-20240327-0059</t>
+  </si>
+  <si>
+    <t>2024 - RUBI - W/M - 20240403 AL 20240430</t>
+  </si>
+  <si>
     <t>NTTSO</t>
   </si>
   <si>
@@ -221,109 +217,126 @@
     <t>PEN</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>PR009291</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
+    <t>Basica/Premium_RUBI-45385-45412-WD12BVC2S6C.ABLGLGP-10</t>
+  </si>
+  <si>
     <t>BILL_TO</t>
   </si>
   <si>
+    <t>PE000820001B</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES RUBI S.A.</t>
+  </si>
+  <si>
+    <t>WD12BVC2S6C.ABLGLGP</t>
+  </si>
+  <si>
+    <t>WD14BVC2S6C.ABLGLGP</t>
+  </si>
+  <si>
+    <t>WD15EG2S.AESGLGP</t>
+  </si>
+  <si>
+    <t>WT19BPB.ABMGLGP</t>
+  </si>
+  <si>
+    <t>PR-NTSO-20240405-0031</t>
+  </si>
+  <si>
+    <t>2024 - RUBI - Cooking - 20240410 AL 20240430</t>
+  </si>
+  <si>
+    <t>Basica/Premium_RUBI-45392-45412-RSG314M.FSTGLPR-8</t>
+  </si>
+  <si>
+    <t>RSG314M.FSTGLPR</t>
+  </si>
+  <si>
+    <t>PR-NTSO-20240416-0005</t>
+  </si>
+  <si>
+    <t>2024 - RUBI - Cooking - 20240422 AL 20240430</t>
+  </si>
+  <si>
+    <t>Basica/Premium_RUBI-45404-45412-MS4296DIR.BBKGLPR-140</t>
+  </si>
+  <si>
+    <t>PR-NTSO-20240416-0006</t>
+  </si>
+  <si>
+    <t>2024 - RUBI - W/M - 20240422 AL 20240430</t>
+  </si>
+  <si>
+    <t>Basica/Premium_RUBI-45404-45412-WT13BPBK.ABMGLGP-40</t>
+  </si>
+  <si>
     <t>WT13BPBK.ABMGLGP</t>
   </si>
   <si>
     <t>WT17BV6.ABMGLGP</t>
   </si>
   <si>
-    <t>PR009291</t>
-  </si>
-  <si>
-    <t>PE000820001B</t>
-  </si>
-  <si>
-    <t>IMPORTACIONES RUBI S.A.</t>
-  </si>
-  <si>
-    <t>WT19BPB.ABMGLGP</t>
-  </si>
-  <si>
-    <t>WD12BVC2S6C.ABLGLGP</t>
-  </si>
-  <si>
-    <t>WD14BVC2S6C.ABLGLGP</t>
-  </si>
-  <si>
-    <t>WD15EG2S.AESGLGP</t>
-  </si>
-  <si>
-    <t>RSG314M.FSTGLPR</t>
-  </si>
-  <si>
-    <t>PR-NTSO-20240327-0059</t>
-  </si>
-  <si>
-    <t>2024 - RUBI - W/M - 20240403 AL 20240430</t>
-  </si>
-  <si>
-    <t>Basica/Premium_RUBI-45385-45412-WD12BVC2S6C.ABLGLGP-10</t>
-  </si>
-  <si>
-    <t>PR-NTSO-20240405-0031</t>
-  </si>
-  <si>
-    <t>2024 - RUBI - Cooking - 20240410 AL 20240430</t>
-  </si>
-  <si>
-    <t>Basica/Premium_RUBI-45392-45412-RSG314M.FSTGLPR-8</t>
-  </si>
-  <si>
-    <t>PR-NTSO-20240416-0005</t>
-  </si>
-  <si>
-    <t>2024 - RUBI - Cooking - 20240422 AL 20240430</t>
-  </si>
-  <si>
-    <t>Basica/Premium_RUBI-45404-45412-MS4296DIR.BBKGLPR-140</t>
-  </si>
-  <si>
-    <t>PR-NTSO-20240416-0006</t>
-  </si>
-  <si>
-    <t>2024 - RUBI - W/M - 20240422 AL 20240430</t>
-  </si>
-  <si>
-    <t>Basica/Premium_RUBI-45404-45412-WT13BPBK.ABMGLGP-40</t>
-  </si>
-  <si>
-    <t>O</t>
+    <t>System msgs: (Remove these messages before upload to GERP)</t>
+  </si>
+  <si>
+    <t>PR-NTSO-20240327-0059 no exists in promotion file.</t>
+  </si>
+  <si>
+    <t>PR-NTSO-20240405-0031 no exists in promotion file.</t>
+  </si>
+  <si>
+    <t>PR-NTSO-20240416-0005 no exists in promotion file.</t>
+  </si>
+  <si>
+    <t>PR-NTSO-20240416-0006 no exists in promotion file.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="###,###,###,##0.##"/>
     <numFmt numFmtId="165" formatCode="###,###,##0.########"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -336,25 +349,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F0F0"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDAA520"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -399,63 +412,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="2" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="2" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="5" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="5" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -502,7 +507,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -537,7 +542,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -581,211 +586,239 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BG9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:BG15"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" customWidth="1"/>
-    <col min="7" max="7" width="32.85546875" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" customWidth="1"/>
-    <col min="12" max="12" width="17.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" customWidth="1"/>
-    <col min="15" max="15" width="28.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="18" width="24.42578125" customWidth="1"/>
-    <col min="19" max="19" width="22.42578125" customWidth="1"/>
-    <col min="20" max="20" width="22.140625" customWidth="1"/>
-    <col min="21" max="21" width="18.42578125" customWidth="1"/>
-    <col min="22" max="22" width="27.7109375" customWidth="1"/>
-    <col min="23" max="23" width="20.42578125" customWidth="1"/>
-    <col min="24" max="24" width="34.140625" customWidth="1"/>
-    <col min="25" max="25" width="24" customWidth="1"/>
-    <col min="26" max="26" width="19" customWidth="1"/>
-    <col min="27" max="27" width="24.140625" customWidth="1"/>
-    <col min="28" max="28" width="28.7109375" customWidth="1"/>
-    <col min="29" max="29" width="21.7109375" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" customWidth="1"/>
-    <col min="31" max="31" width="21" customWidth="1"/>
-    <col min="32" max="32" width="16" customWidth="1"/>
-    <col min="33" max="33" width="16.28515625" customWidth="1"/>
-    <col min="34" max="34" width="22.42578125" customWidth="1"/>
-    <col min="35" max="35" width="23.7109375" customWidth="1"/>
-    <col min="36" max="36" width="19.28515625" customWidth="1"/>
-    <col min="37" max="37" width="23" customWidth="1"/>
-    <col min="38" max="38" width="20.7109375" customWidth="1"/>
-    <col min="39" max="39" width="27.140625" customWidth="1"/>
-    <col min="40" max="40" width="16" customWidth="1"/>
-    <col min="41" max="41" width="17.85546875" customWidth="1"/>
-    <col min="42" max="42" width="16.5703125" customWidth="1"/>
-    <col min="43" max="43" width="15.28515625" customWidth="1"/>
-    <col min="44" max="44" width="16.42578125" customWidth="1"/>
-    <col min="45" max="45" width="17.5703125" customWidth="1"/>
-    <col min="46" max="46" width="17.42578125" customWidth="1"/>
-    <col min="47" max="47" width="17.7109375" customWidth="1"/>
-    <col min="48" max="48" width="25" customWidth="1"/>
-    <col min="49" max="49" width="22.28515625" customWidth="1"/>
-    <col min="50" max="50" width="24.5703125" customWidth="1"/>
-    <col min="51" max="51" width="21.5703125" customWidth="1"/>
-    <col min="52" max="52" width="26.7109375" customWidth="1"/>
-    <col min="53" max="53" width="24.42578125" customWidth="1"/>
-    <col min="54" max="54" width="17.28515625" customWidth="1"/>
-    <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.28515625" customWidth="1"/>
-    <col min="57" max="58" width="22.28515625" customWidth="1"/>
-    <col min="59" max="59" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="19" customWidth="true" style="0"/>
+    <col min="3" max="3" width="17.85546875" customWidth="true" style="0"/>
+    <col min="4" max="4" width="13.85546875" customWidth="true" style="0"/>
+    <col min="5" max="5" width="14.28515625" customWidth="true" style="0"/>
+    <col min="6" max="6" width="29.42578125" customWidth="true" style="0"/>
+    <col min="7" max="7" width="32.85546875" customWidth="true" style="0"/>
+    <col min="8" max="8" width="11.42578125" customWidth="true" style="0"/>
+    <col min="9" max="9" width="24" customWidth="true" style="0"/>
+    <col min="10" max="10" width="14" customWidth="true" style="0"/>
+    <col min="11" max="11" width="24.5703125" customWidth="true" style="0"/>
+    <col min="12" max="12" width="17.28515625" customWidth="true" style="0"/>
+    <col min="13" max="13" width="16" customWidth="true" style="0"/>
+    <col min="14" max="14" width="16.28515625" customWidth="true" style="0"/>
+    <col min="15" max="15" width="28.7109375" customWidth="true" style="0"/>
+    <col min="16" max="16" width="11.5703125" customWidth="true" style="0"/>
+    <col min="17" max="17" width="20.7109375" customWidth="true" style="0"/>
+    <col min="18" max="18" width="24.42578125" customWidth="true" style="0"/>
+    <col min="19" max="19" width="22.42578125" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.140625" customWidth="true" style="0"/>
+    <col min="21" max="21" width="18.42578125" customWidth="true" style="0"/>
+    <col min="22" max="22" width="27.7109375" customWidth="true" style="0"/>
+    <col min="23" max="23" width="20.42578125" customWidth="true" style="0"/>
+    <col min="24" max="24" width="34.140625" customWidth="true" style="0"/>
+    <col min="25" max="25" width="24" customWidth="true" style="0"/>
+    <col min="26" max="26" width="19" customWidth="true" style="0"/>
+    <col min="27" max="27" width="24.140625" customWidth="true" style="0"/>
+    <col min="28" max="28" width="28.7109375" customWidth="true" style="0"/>
+    <col min="29" max="29" width="21.7109375" customWidth="true" style="0"/>
+    <col min="30" max="30" width="13.5703125" customWidth="true" style="0"/>
+    <col min="31" max="31" width="21" customWidth="true" style="0"/>
+    <col min="32" max="32" width="16" customWidth="true" style="0"/>
+    <col min="33" max="33" width="16.28515625" customWidth="true" style="0"/>
+    <col min="34" max="34" width="22.42578125" customWidth="true" style="0"/>
+    <col min="35" max="35" width="23.7109375" customWidth="true" style="0"/>
+    <col min="36" max="36" width="19.28515625" customWidth="true" style="0"/>
+    <col min="37" max="37" width="23" customWidth="true" style="0"/>
+    <col min="38" max="38" width="20.7109375" customWidth="true" style="0"/>
+    <col min="39" max="39" width="27.140625" customWidth="true" style="0"/>
+    <col min="40" max="40" width="16" customWidth="true" style="0"/>
+    <col min="41" max="41" width="17.85546875" customWidth="true" style="0"/>
+    <col min="42" max="42" width="16.5703125" customWidth="true" style="0"/>
+    <col min="43" max="43" width="15.28515625" customWidth="true" style="0"/>
+    <col min="44" max="44" width="16.42578125" customWidth="true" style="0"/>
+    <col min="45" max="45" width="17.5703125" customWidth="true" style="0"/>
+    <col min="46" max="46" width="17.42578125" customWidth="true" style="0"/>
+    <col min="47" max="47" width="17.7109375" customWidth="true" style="0"/>
+    <col min="48" max="48" width="25" customWidth="true" style="0"/>
+    <col min="49" max="49" width="22.28515625" customWidth="true" style="0"/>
+    <col min="50" max="50" width="24.5703125" customWidth="true" style="0"/>
+    <col min="51" max="51" width="21.5703125" customWidth="true" style="0"/>
+    <col min="52" max="52" width="26.7109375" customWidth="true" style="0"/>
+    <col min="53" max="53" width="24.42578125" customWidth="true" style="0"/>
+    <col min="54" max="54" width="17.28515625" customWidth="true" style="0"/>
+    <col min="55" max="55" width="0" hidden="true" customWidth="true" style="0"/>
+    <col min="56" max="56" width="17.28515625" customWidth="true" style="0"/>
+    <col min="57" max="57" width="22.28515625" customWidth="true" style="0"/>
+    <col min="58" max="58" width="22.28515625" customWidth="true" style="0"/>
+    <col min="59" max="59" width="18.28515625" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:59" customHeight="1" ht="22.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -964,12 +997,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:59" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:59" customHeight="1" ht="45">
       <c r="A2" s="5" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
@@ -978,17 +1011,17 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="L2" s="6">
         <v>20240403</v>
@@ -997,28 +1030,28 @@
         <v>20240430</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="S2" s="5">
         <v>20061</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
@@ -1026,30 +1059,30 @@
         <v>6</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
       <c r="AE2" s="5" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG2" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AH2" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK2" s="5"/>
       <c r="AL2" s="6"/>
@@ -1077,7 +1110,7 @@
       <c r="AZ2" s="6"/>
       <c r="BA2" s="6"/>
       <c r="BB2" s="6" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="BC2" s="6"/>
       <c r="BD2" s="6"/>
@@ -1085,12 +1118,12 @@
       <c r="BF2" s="5"/>
       <c r="BG2" s="5"/>
     </row>
-    <row r="3" spans="1:59" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:59" customHeight="1" ht="45">
       <c r="A3" s="10" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C3" s="10">
         <v>2</v>
@@ -1099,17 +1132,17 @@
         <v>1</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="11"/>
       <c r="H3" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
       <c r="K3" s="10" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="L3" s="11">
         <v>20240403</v>
@@ -1118,28 +1151,28 @@
         <v>20240430</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O3" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>60</v>
       </c>
       <c r="S3" s="4">
         <v>20061</v>
       </c>
       <c r="T3" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V3" s="10"/>
       <c r="W3" s="10"/>
@@ -1147,30 +1180,30 @@
         <v>6</v>
       </c>
       <c r="Y3" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z3" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA3" s="10"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="10"/>
       <c r="AD3" s="10"/>
       <c r="AE3" s="10" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AF3" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG3" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AH3" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK3" s="10"/>
       <c r="AL3" s="11"/>
@@ -1198,7 +1231,7 @@
       <c r="AZ3" s="11"/>
       <c r="BA3" s="11"/>
       <c r="BB3" s="11" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="BC3" s="11"/>
       <c r="BD3" s="11"/>
@@ -1206,12 +1239,12 @@
       <c r="BF3" s="10"/>
       <c r="BG3" s="10"/>
     </row>
-    <row r="4" spans="1:59" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:59" customHeight="1" ht="45">
       <c r="A4" s="5" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C4" s="5">
         <v>3</v>
@@ -1220,17 +1253,17 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
       <c r="H4" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="L4" s="6">
         <v>20240403</v>
@@ -1239,28 +1272,28 @@
         <v>20240430</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R4" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="S4" s="5">
         <v>20061</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -1268,30 +1301,30 @@
         <v>6</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA4" s="5"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
       <c r="AE4" s="5" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AH4" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK4" s="5"/>
       <c r="AL4" s="6"/>
@@ -1319,7 +1352,7 @@
       <c r="AZ4" s="6"/>
       <c r="BA4" s="6"/>
       <c r="BB4" s="6" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="BC4" s="6"/>
       <c r="BD4" s="6"/>
@@ -1327,12 +1360,12 @@
       <c r="BF4" s="5"/>
       <c r="BG4" s="5"/>
     </row>
-    <row r="5" spans="1:59" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:59" customHeight="1" ht="45">
       <c r="A5" s="10" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C5" s="10">
         <v>4</v>
@@ -1341,17 +1374,17 @@
         <v>1</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="11"/>
       <c r="H5" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="L5" s="11">
         <v>20240403</v>
@@ -1360,28 +1393,28 @@
         <v>20240430</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="P5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="R5" s="10" t="s">
-        <v>60</v>
       </c>
       <c r="S5" s="4">
         <v>20061</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V5" s="10"/>
       <c r="W5" s="10"/>
@@ -1389,30 +1422,30 @@
         <v>6</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA5" s="10"/>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10"/>
       <c r="AD5" s="10"/>
       <c r="AE5" s="10" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AF5" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG5" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AH5" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AI5" s="4"/>
       <c r="AJ5" s="10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AK5" s="10"/>
       <c r="AL5" s="11"/>
@@ -1440,7 +1473,7 @@
       <c r="AZ5" s="11"/>
       <c r="BA5" s="11"/>
       <c r="BB5" s="11" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="BC5" s="11"/>
       <c r="BD5" s="11"/>
@@ -1448,12 +1481,12 @@
       <c r="BF5" s="10"/>
       <c r="BG5" s="10"/>
     </row>
-    <row r="6" spans="1:59" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:59" customHeight="1" ht="33.75">
       <c r="A6" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -1462,17 +1495,17 @@
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="6"/>
       <c r="H6" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L6" s="6">
         <v>20240410</v>
@@ -1481,28 +1514,28 @@
         <v>20240430</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R6" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="S6" s="5">
         <v>20061</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
@@ -1510,30 +1543,30 @@
         <v>6</v>
       </c>
       <c r="Y6" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA6" s="5"/>
       <c r="AB6" s="5"/>
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK6" s="5"/>
       <c r="AL6" s="6"/>
@@ -1561,7 +1594,7 @@
       <c r="AZ6" s="6"/>
       <c r="BA6" s="6"/>
       <c r="BB6" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BC6" s="6"/>
       <c r="BD6" s="6"/>
@@ -1569,12 +1602,12 @@
       <c r="BF6" s="5"/>
       <c r="BG6" s="5"/>
     </row>
-    <row r="7" spans="1:59" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:59" customHeight="1" ht="45">
       <c r="A7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="C7" s="5">
         <v>2</v>
@@ -1583,17 +1616,17 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6"/>
       <c r="H7" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L7" s="6">
         <v>20240422</v>
@@ -1602,28 +1635,28 @@
         <v>20240430</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R7" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="S7" s="5">
         <v>20061</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
@@ -1631,30 +1664,30 @@
         <v>6</v>
       </c>
       <c r="Y7" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
       <c r="AE7" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG7" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AH7" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK7" s="5"/>
       <c r="AL7" s="6"/>
@@ -1682,7 +1715,7 @@
       <c r="AZ7" s="6"/>
       <c r="BA7" s="6"/>
       <c r="BB7" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BC7" s="6"/>
       <c r="BD7" s="6"/>
@@ -1690,12 +1723,12 @@
       <c r="BF7" s="5"/>
       <c r="BG7" s="5"/>
     </row>
-    <row r="8" spans="1:59" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:59" customHeight="1" ht="33.75">
       <c r="A8" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>86</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
@@ -1704,17 +1737,17 @@
         <v>1</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
       <c r="H8" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L8" s="11">
         <v>20240422</v>
@@ -1723,28 +1756,28 @@
         <v>20240430</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="R8" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>60</v>
       </c>
       <c r="S8" s="4">
         <v>20061</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V8" s="10"/>
       <c r="W8" s="10"/>
@@ -1752,30 +1785,30 @@
         <v>6</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA8" s="10"/>
       <c r="AB8" s="10"/>
       <c r="AC8" s="10"/>
       <c r="AD8" s="10"/>
       <c r="AE8" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF8" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AH8" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AI8" s="4"/>
       <c r="AJ8" s="10" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="AK8" s="10"/>
       <c r="AL8" s="11"/>
@@ -1803,7 +1836,7 @@
       <c r="AZ8" s="11"/>
       <c r="BA8" s="11"/>
       <c r="BB8" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BC8" s="11"/>
       <c r="BD8" s="11"/>
@@ -1811,12 +1844,12 @@
       <c r="BF8" s="10"/>
       <c r="BG8" s="10"/>
     </row>
-    <row r="9" spans="1:59" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:59" customHeight="1" ht="33.75">
       <c r="A9" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="C9" s="5">
         <v>2</v>
@@ -1825,17 +1858,17 @@
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="6"/>
       <c r="H9" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L9" s="6">
         <v>20240422</v>
@@ -1844,28 +1877,28 @@
         <v>20240430</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="S9" s="5">
         <v>20061</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
@@ -1873,30 +1906,30 @@
         <v>6</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AA9" s="5"/>
       <c r="AB9" s="5"/>
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AH9" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="5" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="AK9" s="5"/>
       <c r="AL9" s="6"/>
@@ -1924,7 +1957,7 @@
       <c r="AZ9" s="6"/>
       <c r="BA9" s="6"/>
       <c r="BB9" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BC9" s="6"/>
       <c r="BD9" s="6"/>
@@ -1932,9 +1965,44 @@
       <c r="BF9" s="5"/>
       <c r="BG9" s="5"/>
     </row>
+    <row r="11" spans="1:59">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:59">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:59">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:59">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:59">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:BG9"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>